--- a/output/forecast.xlsx
+++ b/output/forecast.xlsx
@@ -603,242 +603,242 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>0.0208805925791523</v>
+        <v>0.039201355746544</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0417439215673605</v>
+        <v>0.0238778338085761</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0260680109433095</v>
+        <v>0.0122633135266182</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0124354923880415</v>
+        <v>0.00322028065927536</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.00356887096380669</v>
+        <v>0.00611428970375308</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.00576895475809226</v>
+        <v>0.00910958123043116</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0094285722137535</v>
+        <v>0.0162255563832863</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0155956765898135</v>
+        <v>0.0153464261055939</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0153449349187102</v>
+        <v>0.0133242229140394</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0137085970289119</v>
+        <v>0.0178842490994885</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0192194408806185</v>
+        <v>0.0139594679504228</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0151581218118867</v>
+        <v>0.0109370807153482</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0116535162493278</v>
+        <v>0.0188361010717453</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0183448668851387</v>
+        <v>0.0175756452876669</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.0172978185448621</v>
+        <v>0.0149863103294677</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.0152291448571429</v>
+        <v>0.0138109476927603</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.0151037401043819</v>
+        <v>0.00968552109736961</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.0105090880165526</v>
+        <v>0.00791493454076129</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.00809513107510787</v>
+        <v>0.0051736264827301</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.00419074774832226</v>
+        <v>0.00874821681551317</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.00801543887504296</v>
+        <v>0.0109271793139065</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.0110933048571429</v>
+        <v>0.0107359309493157</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.0117123994350022</v>
+        <v>0.00893647231311409</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.0101385607351378</v>
+        <v>0.00824063454879287</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.00905321</v>
+        <v>0.00821393807100047</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.00865715944026681</v>
+        <v>0.0102067657827946</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.0104160284643123</v>
+        <v>0.0111119131259996</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.0114601855730138</v>
+        <v>0.0140162595148781</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.0133818636804546</v>
+        <v>0.0119627701455902</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.0116792224034736</v>
+        <v>0.0104021648315789</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.0102811178584151</v>
+        <v>0.00832044263198439</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.0082127253245658</v>
+        <v>0.00883299322827636</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.00889675396564286</v>
+        <v>0.00944544701222253</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.00978740031042362</v>
+        <v>0.00628174906696502</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.00703975581809884</v>
+        <v>0.00710950159424955</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.00771354664960784</v>
+        <v>0.00826647313541323</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.00870214264866535</v>
+        <v>-0.0108618278166141</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-0.00875171592312186</v>
+        <v>-0.00653165199444238</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-0.00561743247764672</v>
+        <v>0.0000967543965798828</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.0002270391583046</v>
+        <v>0.00244913370036726</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-0.000321818591729358</v>
+        <v>0.0101352872479455</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.00908767423974322</v>
+        <v>0.0135086215817072</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.014189029293438</v>
+        <v>0.02044411018464</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.0213030428469534</v>
+        <v>0.0137050563167719</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.0143012224807507</v>
+        <v>0.00909317734021225</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.00867489831384259</v>
+        <v>0.00467542944969886</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.00337607046743168</v>
+        <v>0.0077008261815744</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.00708890316739596</v>
+        <v>0.0100008276593782</v>
       </c>
     </row>
     <row r="49">
@@ -866,7 +866,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0157673092903483</v>
+        <v>0.0154386076172396</v>
       </c>
     </row>
     <row r="5">
@@ -877,7 +877,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0346048321271051</v>
+        <v>0.013659691874553</v>
       </c>
     </row>
     <row r="8">
@@ -888,7 +888,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0212922964955234</v>
+        <v>0.0147210562606515</v>
       </c>
     </row>
     <row r="11">
@@ -899,7 +899,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0227775548450109</v>
+        <v>0.0187902053728565</v>
       </c>
     </row>
     <row r="14">
@@ -910,7 +910,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.010700609808618</v>
+        <v>0.0169553627125188</v>
       </c>
     </row>
     <row r="17">
@@ -921,7 +921,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.00981375329497534</v>
+        <v>0.017702015361575</v>
       </c>
     </row>
     <row r="20">
@@ -932,7 +932,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.000201914806921973</v>
+        <v>0.0177996761006313</v>
       </c>
     </row>
     <row r="23">
@@ -943,7 +943,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.0134899483812819</v>
+        <v>0.011582472105742</v>
       </c>
     </row>
     <row r="26">
@@ -954,7 +954,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.00410226540317616</v>
+        <v>0.00778810895998739</v>
       </c>
     </row>
     <row r="29">
@@ -965,7 +965,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.0068211392339032</v>
+        <v>0.0147857088629789</v>
       </c>
     </row>
     <row r="32">
@@ -976,7 +976,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.0123808427045609</v>
+        <v>0.0132743582876122</v>
       </c>
     </row>
     <row r="35">
@@ -987,7 +987,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-0.0552564518828218</v>
+        <v>-0.00309077541782634</v>
       </c>
     </row>
     <row r="38">
@@ -998,7 +998,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.0425850395894901</v>
+        <v>0.0108434905333412</v>
       </c>
     </row>
     <row r="41">
@@ -1009,7 +1009,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.00389125483007713</v>
+        <v>0.010683368843575</v>
       </c>
     </row>
     <row r="44">
@@ -1020,7 +1020,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.00052250343620875</v>
+        <v>0.00855271355228642</v>
       </c>
     </row>
     <row r="47">
@@ -1031,7 +1031,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.00861061688263711</v>
+        <v>0.0171450667313933</v>
       </c>
     </row>
   </sheetData>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.00533217771675943</v>
+        <v>0.0117326209820302</v>
       </c>
     </row>
     <row r="5">
@@ -1067,7 +1067,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0396539622290263</v>
+        <v>0.0108960504825199</v>
       </c>
     </row>
     <row r="8">
@@ -1078,7 +1078,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0120737130768321</v>
+        <v>0.0161802896959579</v>
       </c>
     </row>
     <row r="11">
@@ -1089,7 +1089,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0269607840701745</v>
+        <v>0.018865813994737</v>
       </c>
     </row>
     <row r="14">
@@ -1100,7 +1100,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.00705700553244672</v>
+        <v>0.0194895834451105</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.0108504453118194</v>
+        <v>0.0181146635128779</v>
       </c>
     </row>
     <row r="20">
@@ -1122,7 +1122,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.00176780822136012</v>
+        <v>0.0171766330360351</v>
       </c>
     </row>
     <row r="23">
@@ -1133,7 +1133,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.0116711966390539</v>
+        <v>0.0141973969864204</v>
       </c>
     </row>
     <row r="26">
@@ -1144,7 +1144,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.00583168398945792</v>
+        <v>0.00865166573210851</v>
       </c>
     </row>
     <row r="29">
@@ -1155,7 +1155,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.00624105290846388</v>
+        <v>0.0141642234284751</v>
       </c>
     </row>
     <row r="32">
@@ -1166,7 +1166,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.00523310503793818</v>
+        <v>0.015211729534928</v>
       </c>
     </row>
     <row r="35">
@@ -1177,7 +1177,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-0.0556701547941667</v>
+        <v>-0.00936389661164536</v>
       </c>
     </row>
     <row r="38">
@@ -1188,7 +1188,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.0411255903442551</v>
+        <v>0.00943938906387804</v>
       </c>
     </row>
     <row r="41">
@@ -1199,7 +1199,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.00133733604531149</v>
+        <v>0.0106183406935087</v>
       </c>
     </row>
     <row r="44">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.0128701211395183</v>
+        <v>0.00768883773290075</v>
       </c>
     </row>
     <row r="47">
@@ -1221,7 +1221,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.00533196143479599</v>
+        <v>0.0127475748282161</v>
       </c>
     </row>
   </sheetData>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0176754095457005</v>
+        <v>0.00224425051409125</v>
       </c>
     </row>
     <row r="5">
@@ -1257,7 +1257,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0196025185899573</v>
+        <v>0.0118035666760139</v>
       </c>
     </row>
     <row r="8">
@@ -1268,7 +1268,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0195983324827831</v>
+        <v>0.0133111145982076</v>
       </c>
     </row>
     <row r="11">
@@ -1279,7 +1279,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0089881763643626</v>
+        <v>0.0115094421321763</v>
       </c>
     </row>
     <row r="14">
@@ -1290,7 +1290,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.00497620402692445</v>
+        <v>0.00210185036912208</v>
       </c>
     </row>
     <row r="17">
@@ -1301,7 +1301,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.0108796365872164</v>
+        <v>0.0157817199394054</v>
       </c>
     </row>
     <row r="20">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.00756095389863892</v>
+        <v>0.0160173225725187</v>
       </c>
     </row>
     <row r="23">
@@ -1323,7 +1323,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.00892428904108794</v>
+        <v>0.00649367828427385</v>
       </c>
     </row>
     <row r="26">
@@ -1334,7 +1334,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.00280184425762874</v>
+        <v>-0.00656147880518532</v>
       </c>
     </row>
     <row r="29">
@@ -1345,7 +1345,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.00690130193258078</v>
+        <v>0.0120540133077287</v>
       </c>
     </row>
     <row r="32">
@@ -1356,7 +1356,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.00818965452454225</v>
+        <v>0.0139675151322535</v>
       </c>
     </row>
     <row r="35">
@@ -1367,7 +1367,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.00491417880802336</v>
+        <v>-0.00163609476351289</v>
       </c>
     </row>
     <row r="38">
@@ -1378,7 +1378,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.0272884110375443</v>
+        <v>0.00368925767125473</v>
       </c>
     </row>
     <row r="41">
@@ -1389,7 +1389,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.0108515509893779</v>
+        <v>0.00990661223353952</v>
       </c>
     </row>
     <row r="44">
@@ -1400,7 +1400,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.00871304508941177</v>
+        <v>0.0129939038329548</v>
       </c>
     </row>
     <row r="47">
@@ -1411,7 +1411,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.0105652226220984</v>
+        <v>0.0091358992610698</v>
       </c>
     </row>
   </sheetData>
